--- a/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
+++ b/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
@@ -564,44 +564,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>right</t>
@@ -609,12 +609,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -632,16 +632,16 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
         <v>7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -663,57 +663,57 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -724,23 +724,23 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -762,42 +762,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -861,37 +861,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -922,20 +922,20 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
         <v>11</v>
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
       <c r="W6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1059,84 +1059,84 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q7" t="n">
         <v>0.47</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1158,42 +1158,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1226,16 +1226,16 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1257,57 +1257,57 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1318,23 +1318,23 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14</v>
+      </c>
+      <c r="W9" t="n">
         <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>17</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1356,44 +1356,44 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>center</t>
@@ -1401,19 +1401,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
         <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1455,52 +1455,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1509,30 +1509,30 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
         <v>8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>16</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1554,44 +1554,44 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>right</t>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
       <c r="V12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W12" t="n">
         <v>2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1653,27 +1653,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1710,7 +1710,7 @@
         <v>0.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1777,43 +1777,43 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0.4</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1823,13 +1823,13 @@
         <v>11</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1919,16 +1919,16 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2018,16 +2018,16 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="n">
         <v>2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2148,47 +2148,47 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q18" t="n">
         <v>0.2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10</v>
+      </c>
+      <c r="V18" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
       <c r="W18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2247,47 +2247,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2308,23 +2308,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
+        <v>6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>13</v>
+      </c>
+      <c r="W19" t="n">
         <v>4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>16</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2346,84 +2346,84 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q20" t="n">
         <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2490,19 +2490,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -2544,52 +2544,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2605,23 +2605,23 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
         <v>7</v>
       </c>
-      <c r="V22" t="n">
-        <v>9</v>
-      </c>
       <c r="W22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -2643,42 +2643,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2688,16 +2688,16 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>0.47</v>
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2742,52 +2742,52 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2796,30 +2796,30 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q24" t="n">
         <v>0.2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>10</v>
+      </c>
+      <c r="W24" t="n">
         <v>8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>9</v>
-      </c>
-      <c r="V24" t="n">
-        <v>11</v>
-      </c>
-      <c r="W24" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -2841,42 +2841,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2886,16 +2886,16 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0.53</v>
@@ -2909,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" t="n">
         <v>9</v>
       </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
       <c r="V25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2940,27 +2940,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,54 +2970,54 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0.27</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26" t="n">
         <v>11</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3039,22 +3039,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,18 +3089,18 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q27" t="n">
         <v>0.27</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3110,13 +3110,13 @@
         <v>11</v>
       </c>
       <c r="U27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -3138,42 +3138,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -3237,84 +3237,84 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3336,44 +3336,44 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>center</t>
@@ -3381,19 +3381,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3404,16 +3404,16 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
         <v>1</v>
       </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
       <c r="V30" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" t="n">
         <v>8</v>
-      </c>
-      <c r="W30" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -3435,84 +3435,84 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q31" t="n">
         <v>0.53</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
-        <v>3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4</v>
-      </c>
       <c r="W31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -3534,37 +3534,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -3595,20 +3595,20 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S32" t="n">
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
         <v>11</v>
@@ -3633,84 +3633,84 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Q33" t="n">
         <v>0.2</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3732,47 +3732,47 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3782,34 +3782,34 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -3831,42 +3831,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3876,19 +3876,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -3930,32 +3930,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,49 +3965,49 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q36" t="n">
         <v>0.64</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S36" t="n">
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -4029,42 +4029,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4074,19 +4074,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="W37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4128,34 +4128,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>ball</t>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4178,34 +4178,34 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q38" t="n">
         <v>0.33</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
         <v>9</v>
-      </c>
-      <c r="U38" t="n">
-        <v>10</v>
       </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4227,27 +4227,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4272,16 +4272,16 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q39" t="n">
         <v>0.33</v>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U39" t="n">
         <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4351,43 +4351,43 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4397,13 +4397,13 @@
         <v>11</v>
       </c>
       <c r="U40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -4425,42 +4425,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4470,19 +4470,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q41" t="n">
         <v>0.42</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.31</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -4493,16 +4493,16 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U41" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -4524,37 +4524,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4564,41 +4564,41 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P42" t="n">
         <v>0.64</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
         <v>9</v>
@@ -4623,44 +4623,44 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>center</t>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4691,16 +4691,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="n">
-        <v>2</v>
-      </c>
       <c r="V43" t="n">
+        <v>10</v>
+      </c>
+      <c r="W43" t="n">
         <v>7</v>
-      </c>
-      <c r="W43" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -4722,39 +4722,39 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>car</t>
@@ -4762,41 +4762,41 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q44" t="n">
         <v>0.42</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S44" t="n">
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
+        <v>10</v>
+      </c>
+      <c r="V44" t="n">
         <v>3</v>
-      </c>
-      <c r="V44" t="n">
-        <v>4</v>
       </c>
       <c r="W44" t="n">
         <v>11</v>
@@ -4821,44 +4821,44 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>right</t>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
+        <v>10</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" t="n">
+        <v>8</v>
+      </c>
+      <c r="W45" t="n">
         <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>4</v>
-      </c>
-      <c r="V45" t="n">
-        <v>6</v>
-      </c>
-      <c r="W45" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -4920,84 +4920,84 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q46" t="n">
         <v>0.47</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
+        <v>2</v>
+      </c>
+      <c r="V46" t="n">
         <v>5</v>
       </c>
-      <c r="V46" t="n">
-        <v>10</v>
-      </c>
       <c r="W46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -5019,52 +5019,52 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5073,30 +5073,30 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q47" t="n">
         <v>0.27</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5118,52 +5118,52 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5172,30 +5172,30 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S48" t="n">
         <v>9</v>
       </c>
       <c r="T48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>4</v>
+      </c>
+      <c r="W48" t="n">
         <v>6</v>
-      </c>
-      <c r="U48" t="n">
-        <v>7</v>
-      </c>
-      <c r="V48" t="n">
-        <v>10</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5217,52 +5217,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,30 +5271,30 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S49" t="n">
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -5316,84 +5316,84 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S50" t="n">
         <v>11</v>
       </c>
       <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" t="n">
+        <v>11</v>
+      </c>
+      <c r="W50" t="n">
         <v>8</v>
-      </c>
-      <c r="U50" t="n">
-        <v>9</v>
-      </c>
-      <c r="V50" t="n">
-        <v>3</v>
-      </c>
-      <c r="W50" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5465,34 +5465,34 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
+        <v>7</v>
+      </c>
+      <c r="U51" t="n">
         <v>9</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
+        <v>4</v>
+      </c>
+      <c r="W51" t="n">
         <v>10</v>
-      </c>
-      <c r="V51" t="n">
-        <v>2</v>
-      </c>
-      <c r="W51" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -5514,27 +5514,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U52" t="n">
         <v>11</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -5613,22 +5613,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5638,43 +5638,43 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5684,13 +5684,13 @@
         <v>11</v>
       </c>
       <c r="U53" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V53" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="W53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -5712,37 +5712,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -5780,13 +5780,13 @@
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U54" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
         <v>9</v>
@@ -5811,84 +5811,84 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S55" t="n">
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
@@ -5910,42 +5910,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.58</v>
+        <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
         <v>1</v>
       </c>
-      <c r="U56" t="n">
-        <v>2</v>
-      </c>
       <c r="V56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -6009,44 +6009,44 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>left</t>
@@ -6054,19 +6054,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V57" t="n">
+        <v>6</v>
+      </c>
+      <c r="W57" t="n">
         <v>7</v>
-      </c>
-      <c r="W57" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -6108,52 +6108,52 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6162,30 +6162,30 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
+      </c>
+      <c r="V58" t="n">
         <v>3</v>
       </c>
-      <c r="U58" t="n">
-        <v>4</v>
-      </c>
-      <c r="V58" t="n">
-        <v>5</v>
-      </c>
       <c r="W58" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -6207,84 +6207,84 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W59" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -6306,44 +6306,44 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>right</t>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V60" t="n">
+        <v>7</v>
+      </c>
+      <c r="W60" t="n">
         <v>1</v>
-      </c>
-      <c r="W60" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -6405,37 +6405,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6450,19 +6450,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -6473,13 +6473,13 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W61" t="n">
         <v>4</v>
@@ -6504,84 +6504,84 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P62" t="n">
         <v>0.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S62" t="n">
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V62" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -6603,44 +6603,44 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>right</t>
@@ -6648,16 +6648,16 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q63" t="n">
         <v>0.2</v>
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>7</v>
+      </c>
+      <c r="V63" t="n">
+        <v>14</v>
+      </c>
+      <c r="W63" t="n">
         <v>8</v>
-      </c>
-      <c r="U63" t="n">
-        <v>9</v>
-      </c>
-      <c r="V63" t="n">
-        <v>12</v>
-      </c>
-      <c r="W63" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -6702,44 +6702,44 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>left</t>
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>7</v>
+      </c>
+      <c r="U64" t="n">
         <v>9</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
+        <v>13</v>
+      </c>
+      <c r="W64" t="n">
         <v>10</v>
-      </c>
-      <c r="V64" t="n">
-        <v>17</v>
-      </c>
-      <c r="W64" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6855,21 +6855,21 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S65" t="n">
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U65" t="n">
         <v>11</v>
@@ -6878,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="W65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6971,13 +6971,13 @@
         <v>11</v>
       </c>
       <c r="U66" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -6999,42 +6999,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7067,16 +7067,16 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -7098,52 +7098,52 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7152,30 +7152,30 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S68" t="n">
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7242,19 +7242,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
         <v>1</v>
       </c>
-      <c r="U69" t="n">
-        <v>2</v>
-      </c>
       <c r="V69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -7296,42 +7296,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7341,19 +7341,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7364,16 +7364,16 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
+        <v>10</v>
+      </c>
+      <c r="V70" t="n">
         <v>3</v>
       </c>
-      <c r="V70" t="n">
-        <v>4</v>
-      </c>
       <c r="W70" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -7395,37 +7395,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7435,41 +7435,41 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
         <v>7</v>
@@ -7494,47 +7494,47 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -7555,23 +7555,23 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
+      </c>
+      <c r="V72" t="n">
+        <v>13</v>
+      </c>
+      <c r="W72" t="n">
         <v>4</v>
-      </c>
-      <c r="U72" t="n">
-        <v>5</v>
-      </c>
-      <c r="V72" t="n">
-        <v>16</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -7593,84 +7593,84 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S73" t="n">
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V73" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7692,47 +7692,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7742,34 +7742,34 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S74" t="n">
         <v>9</v>
       </c>
       <c r="T74" t="n">
+        <v>8</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5</v>
+      </c>
+      <c r="V74" t="n">
+        <v>15</v>
+      </c>
+      <c r="W74" t="n">
         <v>6</v>
-      </c>
-      <c r="U74" t="n">
-        <v>7</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1</v>
-      </c>
-      <c r="W74" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -7791,37 +7791,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7841,31 +7841,31 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P75" t="n">
         <v>0.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S75" t="n">
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U75" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W75" t="n">
         <v>2</v>
@@ -7890,42 +7890,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U76" t="n">
+        <v>7</v>
+      </c>
+      <c r="V76" t="n">
         <v>9</v>
       </c>
-      <c r="V76" t="n">
-        <v>11</v>
-      </c>
       <c r="W76" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -7989,42 +7989,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_43.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_43.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8034,19 +8034,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
+        <v>7</v>
+      </c>
+      <c r="U77" t="n">
         <v>9</v>
       </c>
-      <c r="U77" t="n">
-        <v>10</v>
-      </c>
       <c r="V77" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_45.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_29.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,54 +8118,54 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S78" t="n">
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U78" t="n">
         <v>11</v>
       </c>
       <c r="V78" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -8187,22 +8187,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/car/car_30.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_16.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_43.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8212,43 +8212,43 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P79" t="n">
         <v>0.73</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8258,13 +8258,13 @@
         <v>11</v>
       </c>
       <c r="U79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
+++ b/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -614,18 +614,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -673,12 +673,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -693,17 +693,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -713,18 +713,18 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,10 +737,10 @@
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -777,7 +777,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -819,7 +819,7 @@
         <v>0.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,38 +891,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,10 +935,10 @@
         <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -970,7 +970,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0.53</v>
@@ -1034,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
         <v>9</v>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,22 +1089,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1113,14 +1113,14 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1198,28 +1198,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0.27</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1232,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0.2</v>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1406,18 +1406,18 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q10" t="n">
         <v>0.4</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1430,7 +1430,7 @@
         <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="Q11" t="n">
         <v>0.2</v>
@@ -1529,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
         <v>8</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0.33</v>
@@ -1628,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="V12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1693,28 +1693,28 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.27</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1727,7 +1727,7 @@
         <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q14" t="n">
         <v>0.4</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1826,7 +1826,7 @@
         <v>15</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
         <v>8</v>
@@ -1891,17 +1891,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2004,14 +2004,14 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2188,28 +2188,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q18" t="n">
         <v>0.2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2222,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
         <v>14</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,18 +2396,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q20" t="n">
         <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,38 +2475,38 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2519,10 +2519,10 @@
         <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,38 +2574,38 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,10 +2618,10 @@
         <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2693,18 +2693,18 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.2</v>
@@ -2816,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2898,11 +2898,11 @@
         <v>0.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2918,7 +2918,7 @@
         <v>11</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2980,28 +2980,28 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q26" t="n">
         <v>0.27</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3014,7 +3014,7 @@
         <v>11</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
         <v>5</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3093,14 +3093,14 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q27" t="n">
         <v>0.27</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,7 +3113,7 @@
         <v>15</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
         <v>3</v>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,17 +3168,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3188,18 +3188,18 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3212,10 +3212,10 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,38 +3267,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3311,10 +3311,10 @@
         <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3390,14 +3390,14 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3410,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3786,14 +3786,14 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3806,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3905,10 +3905,10 @@
         <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,22 +3960,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3984,14 +3984,14 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4074,19 +4074,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4178,18 +4178,18 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="Q38" t="n">
         <v>0.33</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -4202,7 +4202,7 @@
         <v>9</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="W38" t="n">
         <v>2</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4272,16 +4272,16 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q39" t="n">
         <v>0.33</v>
@@ -4301,7 +4301,7 @@
         <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W39" t="n">
         <v>8</v>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4376,18 +4376,18 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q40" t="n">
         <v>0.33</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,7 +4400,7 @@
         <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>5</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4475,18 +4475,18 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q41" t="n">
         <v>0.42</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
         <v>3</v>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4554,22 +4554,22 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4578,14 +4578,14 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4598,10 +4598,10 @@
         <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,38 +4653,38 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,10 +4697,10 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4752,38 +4752,38 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4796,10 +4796,10 @@
         <v>10</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4851,22 +4851,22 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4875,14 +4875,14 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,10 +4895,10 @@
         <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4965,19 +4965,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
         <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5168,18 +5168,18 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q48" t="n">
         <v>0.2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,7 +5192,7 @@
         <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W48" t="n">
         <v>6</v>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         <v>3</v>
       </c>
       <c r="V49" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5356,28 +5356,28 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5390,7 +5390,7 @@
         <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W50" t="n">
         <v>8</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5450,33 +5450,33 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
         <v>0.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5492,7 +5492,7 @@
         <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5554,28 +5554,28 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="Q52" t="n">
         <v>0.27</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,7 +5588,7 @@
         <v>11</v>
       </c>
       <c r="V52" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W52" t="n">
         <v>5</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,38 +5643,38 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5687,10 +5687,10 @@
         <v>15</v>
       </c>
       <c r="V53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W53" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5742,38 +5742,38 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,10 +5786,10 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_37.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_29.jpg</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>chair</t>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>center</t>
@@ -5955,19 +5955,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P56" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0.47</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         <v>1</v>
       </c>
       <c r="V56" t="n">
+        <v>8</v>
+      </c>
+      <c r="W56" t="n">
         <v>7</v>
-      </c>
-      <c r="W56" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6044,33 +6044,33 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
         <v>0.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -6086,7 +6086,7 @@
         <v>6</v>
       </c>
       <c r="W57" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6138,38 +6138,38 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6182,10 +6182,10 @@
         <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6237,38 +6237,38 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6281,10 +6281,10 @@
         <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6346,28 +6346,28 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q60" t="n">
         <v>0.27</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6380,7 +6380,7 @@
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6455,18 +6455,18 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q61" t="n">
         <v>0.4</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6479,7 +6479,7 @@
         <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W61" t="n">
         <v>4</v>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -6578,10 +6578,10 @@
         <v>3</v>
       </c>
       <c r="V62" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,38 +6633,38 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -6677,10 +6677,10 @@
         <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="W63" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,17 +6831,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6851,18 +6851,18 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6875,10 +6875,10 @@
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,33 +6935,33 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P66" t="n">
         <v>0.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6977,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,38 +7029,38 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,22 +7128,22 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7152,14 +7152,14 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7242,19 +7242,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
         <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -7306,14 +7306,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_29.jpg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_29.jpg</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>ball</t>
@@ -7326,22 +7326,22 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7350,14 +7350,14 @@
         </is>
       </c>
       <c r="P70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q70" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.36</v>
-      </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -7370,10 +7370,10 @@
         <v>10</v>
       </c>
       <c r="V70" t="n">
+        <v>6</v>
+      </c>
+      <c r="W70" t="n">
         <v>3</v>
-      </c>
-      <c r="W70" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7440,19 +7440,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="Q73" t="n">
         <v>0.27</v>
@@ -7667,7 +7667,7 @@
         <v>8</v>
       </c>
       <c r="V73" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7727,33 +7727,33 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P74" t="n">
         <v>0.58</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7769,7 +7769,7 @@
         <v>15</v>
       </c>
       <c r="W74" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,38 +7821,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,38 +7920,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7964,10 +7964,10 @@
         <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W76" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,38 +8019,38 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -8063,10 +8063,10 @@
         <v>9</v>
       </c>
       <c r="V77" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8145,7 +8145,7 @@
         <v>0.73</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8232,19 +8232,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8261,10 +8261,10 @@
         <v>15</v>
       </c>
       <c r="V79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W79" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
+++ b/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,38 +594,38 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -678,7 +678,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -698,33 +698,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -740,7 +740,7 @@
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -777,7 +777,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -819,11 +819,11 @@
         <v>0.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -970,7 +970,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1010,18 +1010,18 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q6" t="n">
         <v>0.53</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1034,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>9</v>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,38 +1089,38 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1208,18 +1208,18 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1232,10 +1232,10 @@
         <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,18 +1307,18 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="Q9" t="n">
         <v>0.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,33 +1391,33 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>0.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1433,7 +1433,7 @@
         <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1505,18 +1505,18 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1529,10 +1529,10 @@
         <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1589,33 +1589,33 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>0.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1631,7 +1631,7 @@
         <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1703,18 +1703,18 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1787,33 +1787,33 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P14" t="n">
         <v>0.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1829,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1886,33 +1886,33 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>0.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,38 +1980,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,38 +2079,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,10 +2123,10 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,18 +2396,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q20" t="n">
         <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2495,18 +2495,18 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P21" t="n">
         <v>0.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2522,7 +2522,7 @@
         <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,38 +2673,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,22 +2871,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2895,14 +2895,14 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2915,10 +2915,10 @@
         <v>9</v>
       </c>
       <c r="V25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2997,11 +2997,11 @@
         <v>0.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3017,7 +3017,7 @@
         <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,38 +3168,38 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3212,10 +3212,10 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,38 +3267,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3311,10 +3311,10 @@
         <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3381,19 +3381,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -3475,17 +3475,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3584,18 +3584,18 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3608,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,18 +3683,18 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3707,10 +3707,10 @@
         <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3881,18 +3881,18 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,38 +3960,38 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4069,28 +4069,28 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" t="n">
         <v>0.2</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4103,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W37" t="n">
         <v>8</v>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4267,28 +4267,28 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q39" t="n">
         <v>0.33</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,7 +4301,7 @@
         <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W39" t="n">
         <v>8</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,38 +4356,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,10 +4400,10 @@
         <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W40" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4470,19 +4470,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4574,18 +4574,18 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4598,10 +4598,10 @@
         <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
         <v>0.36</v>
@@ -4697,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W43" t="n">
         <v>11</v>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4871,18 +4871,18 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,10 +4895,10 @@
         <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,38 +4950,38 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4994,10 +4994,10 @@
         <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -5059,17 +5059,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5175,7 +5175,7 @@
         <v>0.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>14</v>
       </c>
       <c r="W48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,22 +5247,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,14 +5271,14 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5291,10 +5291,10 @@
         <v>3</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W49" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5445,38 +5445,38 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5489,10 +5489,10 @@
         <v>9</v>
       </c>
       <c r="V51" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5554,28 +5554,28 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0.27</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,7 +5588,7 @@
         <v>11</v>
       </c>
       <c r="V52" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="W52" t="n">
         <v>5</v>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,33 +5648,33 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P53" t="n">
         <v>0.73</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5690,7 +5690,7 @@
         <v>4</v>
       </c>
       <c r="W53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5752,28 +5752,28 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q54" t="n">
         <v>0.36</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W54" t="n">
         <v>7</v>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5967,7 +5967,7 @@
         <v>0.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>8</v>
       </c>
       <c r="W56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6039,38 +6039,38 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -6083,10 +6083,10 @@
         <v>10</v>
       </c>
       <c r="V57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W57" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6162,14 +6162,14 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6182,10 +6182,10 @@
         <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W58" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6257,18 +6257,18 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6281,10 +6281,10 @@
         <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6360,14 +6360,14 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6380,10 +6380,10 @@
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6450,19 +6450,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W61" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6558,14 +6558,14 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,10 +6578,10 @@
         <v>3</v>
       </c>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6648,19 +6648,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,18 +6752,18 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
         <v>0.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6779,7 +6779,7 @@
         <v>13</v>
       </c>
       <c r="W64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,38 +6831,38 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6875,10 +6875,10 @@
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,38 +6930,38 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,10 +6974,10 @@
         <v>15</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -7009,14 +7009,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_29.jpg</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>guitar</t>
@@ -7029,38 +7029,38 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q67" t="n">
         <v>0.47</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0.31</v>
-      </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
+        <v>4</v>
+      </c>
+      <c r="W67" t="n">
         <v>5</v>
-      </c>
-      <c r="W67" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,38 +7128,38 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,22 +7227,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7251,14 +7251,14 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7271,10 +7271,10 @@
         <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         <v>10</v>
       </c>
       <c r="V70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W70" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/hand/hand_37.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7449,10 +7449,10 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/hammer/hammer_41.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/car/car_02.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7643,18 +7643,18 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7667,10 +7667,10 @@
         <v>8</v>
       </c>
       <c r="V73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7742,18 +7742,18 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7766,10 +7766,10 @@
         <v>5</v>
       </c>
       <c r="V74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W74" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,38 +7821,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W75" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>stimuli/house/house_29.jpg</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>stimuli/key/key_29.jpg</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_37.jpg</t>
-        </is>
-      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>bread</t>
@@ -7920,38 +7920,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P76" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q76" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7964,10 +7964,10 @@
         <v>7</v>
       </c>
       <c r="V76" t="n">
+        <v>9</v>
+      </c>
+      <c r="W76" t="n">
         <v>15</v>
-      </c>
-      <c r="W76" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/lamp/lamp_05.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8034,19 +8034,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
         <v>9</v>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8118,22 +8118,22 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -8142,14 +8142,14 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -8162,10 +8162,10 @@
         <v>11</v>
       </c>
       <c r="V78" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/guitar/guitar_02.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8244,7 +8244,7 @@
         <v>0.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>1</v>
       </c>
       <c r="W79" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
+++ b/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>7</v>
@@ -668,17 +668,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -734,13 +734,13 @@
         <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -762,12 +762,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -830,10 +830,10 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
         <v>11</v>
@@ -965,19 +965,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>stimuli/house/house_29.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_01.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_29.jpg</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -985,17 +985,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1031,13 +1031,13 @@
         <v>10</v>
       </c>
       <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="n">
         <v>6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1059,19 +1059,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>stimuli/house/house_29.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_29.jpg</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>stimuli/key/key_29.jpg</t>
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9</v>
       </c>
       <c r="W7" t="n">
         <v>15</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
         <v>8</v>
@@ -1235,7 +1235,7 @@
         <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1328,13 +1328,13 @@
         <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>14</v>
@@ -1455,42 +1455,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_41.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_02.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,7 +1523,7 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>7</v>
@@ -1532,7 +1532,7 @@
         <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1625,10 +1625,10 @@
         <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
         <v>8</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1762,14 +1762,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>car</t>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1826,10 +1826,10 @@
         <v>15</v>
       </c>
       <c r="V14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" t="n">
         <v>4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>7</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>stimuli/key/key_29.jpg</t>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>14</v>
       </c>
       <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
         <v>4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
       </c>
       <c r="W16" t="n">
         <v>15</v>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2216,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2318,13 +2318,13 @@
         <v>10</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
         <v>13</v>
       </c>
       <c r="W19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2414,16 +2414,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
         <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_37.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_37.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_01.jpg</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2615,13 +2615,13 @@
         <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>11</v>
       </c>
       <c r="W22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2711,10 +2711,10 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>7</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2810,13 +2810,13 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2912,13 +2912,13 @@
         <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
         <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
         <v>11</v>
       </c>
       <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
         <v>4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3113,10 +3113,10 @@
         <v>15</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
         <v>11</v>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3308,10 +3308,10 @@
         <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -3336,12 +3336,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3404,10 +3404,10 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
         <v>8</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
         <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W31" t="n">
         <v>11</v>
@@ -3539,19 +3539,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>stimuli/house/house_29.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_29.jpg</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -3559,17 +3559,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3605,13 +3605,13 @@
         <v>10</v>
       </c>
       <c r="U32" t="n">
+        <v>9</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4</v>
+      </c>
+      <c r="W32" t="n">
         <v>6</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
-      <c r="W32" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>15</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3800,7 +3800,7 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
         <v>8</v>
@@ -3809,7 +3809,7 @@
         <v>13</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -3836,19 +3836,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_29.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_29.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>hand</t>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3902,13 +3902,13 @@
         <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
         <v>15</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>14</v>
       </c>
       <c r="W36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4097,7 +4097,7 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>7</v>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4199,13 +4199,13 @@
         <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V38" t="n">
         <v>13</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4295,13 +4295,13 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U39" t="n">
         <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W39" t="n">
         <v>8</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4502,7 +4502,7 @@
         <v>10</v>
       </c>
       <c r="W41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4595,10 +4595,10 @@
         <v>14</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
         <v>15</v>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4691,10 +4691,10 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>10</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>10</v>
       </c>
       <c r="V44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
         <v>7</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>10</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
         <v>11</v>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4988,10 +4988,10 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V46" t="n">
         <v>11</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5087,13 +5087,13 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
         <v>10</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5189,13 +5189,13 @@
         <v>8</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
         <v>14</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
         <v>7</v>
       </c>
       <c r="W49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5384,7 +5384,7 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
         <v>7</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5486,13 +5486,13 @@
         <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V51" t="n">
         <v>14</v>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U52" t="n">
         <v>11</v>
@@ -5591,7 +5591,7 @@
         <v>13</v>
       </c>
       <c r="W52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5687,10 +5687,10 @@
         <v>15</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" t="n">
         <v>15</v>
@@ -5910,12 +5910,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
         <v>8</v>
       </c>
       <c r="W56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6019,17 +6019,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_01.jpg</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
         <v>10</v>
       </c>
       <c r="V57" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" t="n">
         <v>2</v>
-      </c>
-      <c r="W57" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -6113,19 +6113,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>stimuli/house/house_29.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_29.jpg</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -6133,17 +6133,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6179,13 +6179,13 @@
         <v>10</v>
       </c>
       <c r="U58" t="n">
+        <v>9</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>6</v>
-      </c>
-      <c r="V58" t="n">
-        <v>5</v>
-      </c>
-      <c r="W58" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6275,10 +6275,10 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
         <v>8</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6374,13 +6374,13 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U60" t="n">
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W60" t="n">
         <v>10</v>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6476,10 +6476,10 @@
         <v>8</v>
       </c>
       <c r="U61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W61" t="n">
         <v>13</v>
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U62" t="n">
+        <v>2</v>
+      </c>
+      <c r="V62" t="n">
         <v>3</v>
       </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
       <c r="W62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_41.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_05.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,7 +6671,7 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
         <v>7</v>
@@ -6680,7 +6680,7 @@
         <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -6707,19 +6707,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_29.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_02.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_29.jpg</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6773,13 +6773,13 @@
         <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
         <v>13</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U65" t="n">
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7169,7 +7169,7 @@
         <v>14</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V68" t="n">
         <v>10</v>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7265,10 +7265,10 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
         <v>8</v>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7364,13 +7364,13 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U70" t="n">
         <v>10</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" t="n">
         <v>15</v>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7466,7 +7466,7 @@
         <v>10</v>
       </c>
       <c r="U71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V71" t="n">
         <v>8</v>
@@ -7494,12 +7494,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
         <v>13</v>
       </c>
       <c r="W72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7661,7 +7661,7 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U73" t="n">
         <v>8</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7763,13 +7763,13 @@
         <v>8</v>
       </c>
       <c r="U74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>13</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_01.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
-        </is>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
+      </c>
+      <c r="V75" t="n">
         <v>5</v>
       </c>
-      <c r="U75" t="n">
-        <v>3</v>
-      </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>4</v>
-      </c>
-      <c r="W75" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_46.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7958,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
         <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W76" t="n">
         <v>15</v>
@@ -7994,19 +7994,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_29.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_05.jpg</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>stimuli/house/house_29.jpg</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_29.jpg</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -8014,17 +8014,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8060,13 +8060,13 @@
         <v>7</v>
       </c>
       <c r="U77" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V77" t="n">
         <v>14</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/flower/flower_29.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8156,13 +8156,13 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U78" t="n">
         <v>11</v>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W78" t="n">
         <v>10</v>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>15</v>
       </c>
       <c r="V79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W79" t="n">
         <v>13</v>

--- a/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
+++ b/psychopy_exp_files/sequences/learning_block1_fixed-middle-10_16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:AI79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,20 +526,80 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>buf1Concept</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>buf1Exemplar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>buf1File</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>buf2Concept</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>buf2Exemplar</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>buf2File</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>buf13Concept</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>buf13Exemplar</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>buf13File</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>buf14Concept</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>buf14Exemplar</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>buf14File</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>promptTrigNumber</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>correctTrigNumber</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dist01TrigNumber</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dist02TrigNumber</t>
         </is>
@@ -564,27 +624,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -631,16 +691,68 @@
       <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>13</v>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
         <v>14</v>
       </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -663,22 +775,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -730,16 +842,68 @@
       <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AG3" t="n">
         <v>5</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>9</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -762,22 +926,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -829,16 +993,68 @@
       <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AG4" t="n">
         <v>3</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>10</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AI4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -861,22 +1077,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,7 +1112,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,17 +1144,69 @@
       <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>10</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>4</v>
       </c>
-      <c r="W5" t="n">
-        <v>11</v>
+      <c r="AI5" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -960,22 +1228,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1027,16 +1295,68 @@
       <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
         <v>10</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>9</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>2</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1059,22 +1379,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1094,7 +1414,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1126,17 +1446,69 @@
       <c r="S7" t="n">
         <v>7</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>4</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>6</v>
       </c>
-      <c r="W7" t="n">
-        <v>15</v>
+      <c r="AI7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1158,22 +1530,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,7 +1560,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1225,16 +1597,68 @@
       <c r="S8" t="n">
         <v>8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>8</v>
       </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1257,22 +1681,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1711,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1324,16 +1748,68 @@
       <c r="S9" t="n">
         <v>9</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
         <v>8</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1356,22 +1832,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1423,16 +1899,68 @@
       <c r="S10" t="n">
         <v>10</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>14</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1455,22 +1983,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +2013,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1522,16 +2050,68 @@
       <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AG11" t="n">
         <v>7</v>
       </c>
-      <c r="V11" t="n">
-        <v>13</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AH11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1554,22 +2134,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1621,16 +2201,68 @@
       <c r="S12" t="n">
         <v>12</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AG12" t="n">
         <v>6</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AH12" t="n">
         <v>5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AI12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1653,22 +2285,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1678,7 +2310,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1720,16 +2352,68 @@
       <c r="S13" t="n">
         <v>13</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>11</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="AG13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH13" t="n">
         <v>14</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AI13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1752,32 +2436,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1819,16 +2503,68 @@
       <c r="S14" t="n">
         <v>14</v>
       </c>
-      <c r="T14" t="n">
-        <v>11</v>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U14" t="n">
-        <v>15</v>
-      </c>
-      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH14" t="n">
         <v>5</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AI14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1851,27 +2587,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1918,16 +2654,68 @@
       <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
-        <v>13</v>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG15" t="n">
         <v>14</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AH15" t="n">
         <v>3</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AI15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1950,22 +2738,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1985,7 +2773,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2017,17 +2805,69 @@
       <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>14</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AG16" t="n">
         <v>5</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AH16" t="n">
         <v>4</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
+      <c r="AI16" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -2049,22 +2889,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2116,16 +2956,68 @@
       <c r="S17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AG17" t="n">
         <v>3</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AH17" t="n">
         <v>10</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AI17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2148,22 +3040,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,12 +3070,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2215,17 +3107,69 @@
       <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AG18" t="n">
         <v>10</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AH18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI18" t="n">
         <v>11</v>
-      </c>
-      <c r="W18" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2247,22 +3191,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2277,7 +3221,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2314,16 +3258,68 @@
       <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
         <v>10</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AG19" t="n">
         <v>9</v>
       </c>
-      <c r="V19" t="n">
-        <v>13</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AH19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2346,22 +3342,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2413,16 +3409,68 @@
       <c r="S20" t="n">
         <v>7</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AG20" t="n">
         <v>4</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AH20" t="n">
         <v>14</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AI20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2445,22 +3493,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2512,16 +3560,68 @@
       <c r="S21" t="n">
         <v>8</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
         <v>4</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AG21" t="n">
         <v>8</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AH21" t="n">
         <v>2</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AI21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2544,22 +3644,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,7 +3674,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2611,16 +3711,68 @@
       <c r="S22" t="n">
         <v>9</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
         <v>8</v>
       </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI22" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2643,22 +3795,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2678,7 +3830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2710,17 +3862,69 @@
       <c r="S23" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AH23" t="n">
         <v>7</v>
       </c>
-      <c r="W23" t="n">
-        <v>11</v>
+      <c r="AI23" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -2742,22 +3946,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2809,16 +4013,68 @@
       <c r="S24" t="n">
         <v>11</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AG24" t="n">
         <v>7</v>
       </c>
-      <c r="V24" t="n">
+      <c r="AH24" t="n">
         <v>6</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AI24" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2841,22 +4097,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,7 +4127,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2908,16 +4164,68 @@
       <c r="S25" t="n">
         <v>12</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
         <v>7</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AG25" t="n">
         <v>6</v>
       </c>
-      <c r="V25" t="n">
-        <v>15</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2940,22 +4248,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2965,7 +4273,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3007,16 +4315,68 @@
       <c r="S26" t="n">
         <v>13</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>11</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="AG26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH26" t="n">
         <v>5</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AI26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3039,32 +4399,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3106,16 +4466,68 @@
       <c r="S27" t="n">
         <v>14</v>
       </c>
-      <c r="T27" t="n">
-        <v>11</v>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
-      </c>
-      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH27" t="n">
         <v>9</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AI27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3138,27 +4550,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3173,7 +4585,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3205,17 +4617,69 @@
       <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
-        <v>13</v>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG28" t="n">
         <v>14</v>
       </c>
-      <c r="V28" t="n">
+      <c r="AH28" t="n">
         <v>4</v>
       </c>
-      <c r="W28" t="n">
-        <v>11</v>
+      <c r="AI28" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -3237,22 +4701,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3304,16 +4768,68 @@
       <c r="S29" t="n">
         <v>3</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
         <v>14</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AG29" t="n">
         <v>5</v>
       </c>
-      <c r="V29" t="n">
+      <c r="AH29" t="n">
         <v>9</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AI29" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3336,22 +4852,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3371,7 +4887,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3403,17 +4919,69 @@
       <c r="S30" t="n">
         <v>4</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
         <v>5</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AG30" t="n">
         <v>3</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AH30" t="n">
         <v>8</v>
       </c>
-      <c r="W30" t="n">
-        <v>15</v>
+      <c r="AI30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -3435,22 +5003,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3470,7 +5038,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3502,17 +5070,69 @@
       <c r="S31" t="n">
         <v>5</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
         <v>3</v>
       </c>
-      <c r="U31" t="n">
+      <c r="AG31" t="n">
         <v>10</v>
       </c>
-      <c r="V31" t="n">
+      <c r="AH31" t="n">
         <v>2</v>
       </c>
-      <c r="W31" t="n">
-        <v>11</v>
+      <c r="AI31" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -3534,22 +5154,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3601,16 +5221,68 @@
       <c r="S32" t="n">
         <v>6</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
         <v>10</v>
       </c>
-      <c r="U32" t="n">
+      <c r="AG32" t="n">
         <v>9</v>
       </c>
-      <c r="V32" t="n">
+      <c r="AH32" t="n">
         <v>4</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AI32" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3633,22 +5305,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3668,7 +5340,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3700,17 +5372,69 @@
       <c r="S33" t="n">
         <v>7</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
         <v>9</v>
       </c>
-      <c r="U33" t="n">
+      <c r="AG33" t="n">
         <v>4</v>
       </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>15</v>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -3732,22 +5456,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,7 +5486,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3799,16 +5523,68 @@
       <c r="S34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
         <v>4</v>
       </c>
-      <c r="U34" t="n">
+      <c r="AG34" t="n">
         <v>8</v>
       </c>
-      <c r="V34" t="n">
-        <v>13</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="AH34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI34" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3831,22 +5607,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,7 +5637,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3898,16 +5674,68 @@
       <c r="S35" t="n">
         <v>9</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
         <v>8</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>15</v>
-      </c>
-      <c r="W35" t="n">
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI35" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3930,22 +5758,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3997,16 +5825,68 @@
       <c r="S36" t="n">
         <v>10</v>
       </c>
-      <c r="T36" t="n">
-        <v>1</v>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
         <v>2</v>
       </c>
-      <c r="V36" t="n">
+      <c r="AH36" t="n">
         <v>14</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AI36" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4029,22 +5909,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4096,16 +5976,68 @@
       <c r="S37" t="n">
         <v>11</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
         <v>2</v>
       </c>
-      <c r="U37" t="n">
+      <c r="AG37" t="n">
         <v>7</v>
       </c>
-      <c r="V37" t="n">
+      <c r="AH37" t="n">
         <v>10</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AI37" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4128,22 +6060,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4158,7 +6090,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4195,16 +6127,68 @@
       <c r="S38" t="n">
         <v>12</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
         <v>7</v>
       </c>
-      <c r="U38" t="n">
+      <c r="AG38" t="n">
         <v>6</v>
       </c>
-      <c r="V38" t="n">
-        <v>13</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="AH38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI38" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4227,22 +6211,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4252,7 +6236,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4294,16 +6278,68 @@
       <c r="S39" t="n">
         <v>13</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
         <v>6</v>
       </c>
-      <c r="U39" t="n">
-        <v>11</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="AG39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH39" t="n">
         <v>3</v>
       </c>
-      <c r="W39" t="n">
+      <c r="AI39" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4326,42 +6362,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4393,17 +6429,69 @@
       <c r="S40" t="n">
         <v>14</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI40" t="n">
         <v>11</v>
-      </c>
-      <c r="U40" t="n">
-        <v>15</v>
-      </c>
-      <c r="V40" t="n">
-        <v>14</v>
-      </c>
-      <c r="W40" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -4425,27 +6513,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4492,16 +6580,68 @@
       <c r="S41" t="n">
         <v>2</v>
       </c>
-      <c r="T41" t="n">
-        <v>13</v>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG41" t="n">
         <v>14</v>
       </c>
-      <c r="V41" t="n">
+      <c r="AH41" t="n">
         <v>10</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AI41" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4524,22 +6664,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4559,7 +6699,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4591,17 +6731,69 @@
       <c r="S42" t="n">
         <v>3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
         <v>14</v>
       </c>
-      <c r="U42" t="n">
+      <c r="AG42" t="n">
         <v>5</v>
       </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15</v>
+      <c r="AH42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -4623,22 +6815,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4658,7 +6850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4690,17 +6882,69 @@
       <c r="S43" t="n">
         <v>4</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
         <v>5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="AG43" t="n">
         <v>3</v>
       </c>
-      <c r="V43" t="n">
+      <c r="AH43" t="n">
         <v>10</v>
       </c>
-      <c r="W43" t="n">
-        <v>11</v>
+      <c r="AI43" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -4722,22 +6966,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4789,16 +7033,68 @@
       <c r="S44" t="n">
         <v>5</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
         <v>3</v>
       </c>
-      <c r="U44" t="n">
+      <c r="AG44" t="n">
         <v>10</v>
       </c>
-      <c r="V44" t="n">
+      <c r="AH44" t="n">
         <v>4</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AI44" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4821,22 +7117,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4856,7 +7152,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4888,17 +7184,69 @@
       <c r="S45" t="n">
         <v>6</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
         <v>10</v>
       </c>
-      <c r="U45" t="n">
+      <c r="AG45" t="n">
         <v>9</v>
       </c>
-      <c r="V45" t="n">
+      <c r="AH45" t="n">
         <v>2</v>
       </c>
-      <c r="W45" t="n">
-        <v>11</v>
+      <c r="AI45" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -4920,22 +7268,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,12 +7298,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4987,17 +7335,69 @@
       <c r="S46" t="n">
         <v>7</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
         <v>9</v>
       </c>
-      <c r="U46" t="n">
+      <c r="AG46" t="n">
         <v>4</v>
       </c>
-      <c r="V46" t="n">
+      <c r="AH46" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI46" t="n">
         <v>11</v>
-      </c>
-      <c r="W46" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -5019,22 +7419,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5086,16 +7486,68 @@
       <c r="S47" t="n">
         <v>8</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
         <v>4</v>
       </c>
-      <c r="U47" t="n">
+      <c r="AG47" t="n">
         <v>8</v>
       </c>
-      <c r="V47" t="n">
+      <c r="AH47" t="n">
         <v>5</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AI47" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5118,22 +7570,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5185,16 +7637,68 @@
       <c r="S48" t="n">
         <v>9</v>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
         <v>8</v>
       </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="n">
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
         <v>14</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AI48" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5217,22 +7721,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5284,16 +7788,68 @@
       <c r="S49" t="n">
         <v>10</v>
       </c>
-      <c r="T49" t="n">
-        <v>1</v>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2</v>
       </c>
-      <c r="V49" t="n">
+      <c r="AH49" t="n">
         <v>7</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AI49" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5316,22 +7872,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5346,7 +7902,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5383,16 +7939,68 @@
       <c r="S50" t="n">
         <v>11</v>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF50" t="n">
         <v>2</v>
       </c>
-      <c r="U50" t="n">
+      <c r="AG50" t="n">
         <v>7</v>
       </c>
-      <c r="V50" t="n">
-        <v>13</v>
-      </c>
-      <c r="W50" t="n">
+      <c r="AH50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI50" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5415,22 +8023,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5482,16 +8090,68 @@
       <c r="S51" t="n">
         <v>12</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
         <v>7</v>
       </c>
-      <c r="U51" t="n">
+      <c r="AG51" t="n">
         <v>6</v>
       </c>
-      <c r="V51" t="n">
+      <c r="AH51" t="n">
         <v>14</v>
       </c>
-      <c r="W51" t="n">
+      <c r="AI51" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5514,22 +8174,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5539,12 +8199,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5581,16 +8241,68 @@
       <c r="S52" t="n">
         <v>13</v>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF52" t="n">
         <v>6</v>
       </c>
-      <c r="U52" t="n">
+      <c r="AG52" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH52" t="n">
         <v>11</v>
       </c>
-      <c r="V52" t="n">
-        <v>13</v>
-      </c>
-      <c r="W52" t="n">
+      <c r="AI52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5613,32 +8325,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5680,16 +8392,68 @@
       <c r="S53" t="n">
         <v>14</v>
       </c>
-      <c r="T53" t="n">
-        <v>11</v>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U53" t="n">
-        <v>15</v>
-      </c>
-      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH53" t="n">
         <v>5</v>
       </c>
-      <c r="W53" t="n">
+      <c r="AI53" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5712,27 +8476,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5779,16 +8543,68 @@
       <c r="S54" t="n">
         <v>2</v>
       </c>
-      <c r="T54" t="n">
-        <v>13</v>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG54" t="n">
         <v>14</v>
       </c>
-      <c r="V54" t="n">
+      <c r="AH54" t="n">
         <v>10</v>
       </c>
-      <c r="W54" t="n">
+      <c r="AI54" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5811,22 +8627,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5846,7 +8662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5878,17 +8694,69 @@
       <c r="S55" t="n">
         <v>3</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
         <v>14</v>
       </c>
-      <c r="U55" t="n">
+      <c r="AG55" t="n">
         <v>5</v>
       </c>
-      <c r="V55" t="n">
+      <c r="AH55" t="n">
         <v>2</v>
       </c>
-      <c r="W55" t="n">
-        <v>15</v>
+      <c r="AI55" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -5910,22 +8778,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5977,16 +8845,68 @@
       <c r="S56" t="n">
         <v>4</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF56" t="n">
         <v>5</v>
       </c>
-      <c r="U56" t="n">
+      <c r="AG56" t="n">
         <v>3</v>
       </c>
-      <c r="V56" t="n">
+      <c r="AH56" t="n">
         <v>8</v>
       </c>
-      <c r="W56" t="n">
+      <c r="AI56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6009,22 +8929,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6076,16 +8996,68 @@
       <c r="S57" t="n">
         <v>5</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF57" t="n">
         <v>3</v>
       </c>
-      <c r="U57" t="n">
+      <c r="AG57" t="n">
         <v>10</v>
       </c>
-      <c r="V57" t="n">
+      <c r="AH57" t="n">
         <v>4</v>
       </c>
-      <c r="W57" t="n">
+      <c r="AI57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6108,22 +9080,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6175,16 +9147,68 @@
       <c r="S58" t="n">
         <v>6</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF58" t="n">
         <v>10</v>
       </c>
-      <c r="U58" t="n">
+      <c r="AG58" t="n">
         <v>9</v>
       </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="W58" t="n">
+      <c r="AH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI58" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6207,22 +9231,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6242,7 +9266,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6274,17 +9298,69 @@
       <c r="S59" t="n">
         <v>7</v>
       </c>
-      <c r="T59" t="n">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF59" t="n">
         <v>9</v>
       </c>
-      <c r="U59" t="n">
+      <c r="AG59" t="n">
         <v>4</v>
       </c>
-      <c r="V59" t="n">
+      <c r="AH59" t="n">
         <v>8</v>
       </c>
-      <c r="W59" t="n">
-        <v>11</v>
+      <c r="AI59" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -6306,22 +9382,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6373,16 +9449,68 @@
       <c r="S60" t="n">
         <v>8</v>
       </c>
-      <c r="T60" t="n">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
         <v>4</v>
       </c>
-      <c r="U60" t="n">
+      <c r="AG60" t="n">
         <v>8</v>
       </c>
-      <c r="V60" t="n">
+      <c r="AH60" t="n">
         <v>5</v>
       </c>
-      <c r="W60" t="n">
+      <c r="AI60" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6405,22 +9533,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6440,7 +9568,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6472,17 +9600,69 @@
       <c r="S61" t="n">
         <v>9</v>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF61" t="n">
         <v>8</v>
       </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="n">
+      <c r="AG61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH61" t="n">
         <v>6</v>
       </c>
-      <c r="W61" t="n">
-        <v>13</v>
+      <c r="AI61" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="62">
@@ -6504,22 +9684,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6571,16 +9751,68 @@
       <c r="S62" t="n">
         <v>10</v>
       </c>
-      <c r="T62" t="n">
-        <v>1</v>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
         <v>2</v>
       </c>
-      <c r="V62" t="n">
+      <c r="AH62" t="n">
         <v>3</v>
       </c>
-      <c r="W62" t="n">
+      <c r="AI62" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6603,22 +9835,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6670,16 +9902,68 @@
       <c r="S63" t="n">
         <v>11</v>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF63" t="n">
         <v>2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="AG63" t="n">
         <v>7</v>
       </c>
-      <c r="V63" t="n">
+      <c r="AH63" t="n">
         <v>14</v>
       </c>
-      <c r="W63" t="n">
+      <c r="AI63" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6702,22 +9986,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6732,7 +10016,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6769,16 +10053,68 @@
       <c r="S64" t="n">
         <v>12</v>
       </c>
-      <c r="T64" t="n">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
         <v>7</v>
       </c>
-      <c r="U64" t="n">
+      <c r="AG64" t="n">
         <v>6</v>
       </c>
-      <c r="V64" t="n">
-        <v>13</v>
-      </c>
-      <c r="W64" t="n">
+      <c r="AH64" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI64" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6801,22 +10137,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6826,7 +10162,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6868,16 +10204,68 @@
       <c r="S65" t="n">
         <v>13</v>
       </c>
-      <c r="T65" t="n">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF65" t="n">
         <v>6</v>
       </c>
-      <c r="U65" t="n">
-        <v>11</v>
-      </c>
-      <c r="V65" t="n">
+      <c r="AG65" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH65" t="n">
         <v>3</v>
       </c>
-      <c r="W65" t="n">
+      <c r="AI65" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6900,32 +10288,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6967,16 +10355,68 @@
       <c r="S66" t="n">
         <v>14</v>
       </c>
-      <c r="T66" t="n">
-        <v>11</v>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U66" t="n">
-        <v>15</v>
-      </c>
-      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH66" t="n">
         <v>14</v>
       </c>
-      <c r="W66" t="n">
+      <c r="AI66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6999,27 +10439,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7066,16 +10506,68 @@
       <c r="S67" t="n">
         <v>2</v>
       </c>
-      <c r="T67" t="n">
-        <v>13</v>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG67" t="n">
         <v>14</v>
       </c>
-      <c r="V67" t="n">
+      <c r="AH67" t="n">
         <v>5</v>
       </c>
-      <c r="W67" t="n">
+      <c r="AI67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7098,22 +10590,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7133,7 +10625,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7165,17 +10657,69 @@
       <c r="S68" t="n">
         <v>3</v>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF68" t="n">
         <v>14</v>
       </c>
-      <c r="U68" t="n">
+      <c r="AG68" t="n">
         <v>5</v>
       </c>
-      <c r="V68" t="n">
+      <c r="AH68" t="n">
         <v>10</v>
       </c>
-      <c r="W68" t="n">
-        <v>15</v>
+      <c r="AI68" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -7197,22 +10741,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7232,7 +10776,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7264,17 +10808,69 @@
       <c r="S69" t="n">
         <v>4</v>
       </c>
-      <c r="T69" t="n">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF69" t="n">
         <v>5</v>
       </c>
-      <c r="U69" t="n">
+      <c r="AG69" t="n">
         <v>3</v>
       </c>
-      <c r="V69" t="n">
+      <c r="AH69" t="n">
         <v>8</v>
       </c>
-      <c r="W69" t="n">
-        <v>11</v>
+      <c r="AI69" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -7296,22 +10892,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7331,7 +10927,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7363,17 +10959,69 @@
       <c r="S70" t="n">
         <v>5</v>
       </c>
-      <c r="T70" t="n">
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF70" t="n">
         <v>3</v>
       </c>
-      <c r="U70" t="n">
+      <c r="AG70" t="n">
         <v>10</v>
       </c>
-      <c r="V70" t="n">
+      <c r="AH70" t="n">
         <v>2</v>
       </c>
-      <c r="W70" t="n">
-        <v>15</v>
+      <c r="AI70" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -7395,22 +11043,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7462,16 +11110,68 @@
       <c r="S71" t="n">
         <v>6</v>
       </c>
-      <c r="T71" t="n">
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF71" t="n">
         <v>10</v>
       </c>
-      <c r="U71" t="n">
+      <c r="AG71" t="n">
         <v>9</v>
       </c>
-      <c r="V71" t="n">
+      <c r="AH71" t="n">
         <v>8</v>
       </c>
-      <c r="W71" t="n">
+      <c r="AI71" t="n">
         <v>14</v>
       </c>
     </row>
@@ -7494,22 +11194,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7524,7 +11224,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7561,16 +11261,68 @@
       <c r="S72" t="n">
         <v>7</v>
       </c>
-      <c r="T72" t="n">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF72" t="n">
         <v>9</v>
       </c>
-      <c r="U72" t="n">
+      <c r="AG72" t="n">
         <v>4</v>
       </c>
-      <c r="V72" t="n">
-        <v>13</v>
-      </c>
-      <c r="W72" t="n">
+      <c r="AH72" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI72" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7593,22 +11345,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7628,7 +11380,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7660,17 +11412,69 @@
       <c r="S73" t="n">
         <v>8</v>
       </c>
-      <c r="T73" t="n">
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF73" t="n">
         <v>4</v>
       </c>
-      <c r="U73" t="n">
+      <c r="AG73" t="n">
         <v>8</v>
       </c>
-      <c r="V73" t="n">
+      <c r="AH73" t="n">
         <v>7</v>
       </c>
-      <c r="W73" t="n">
-        <v>11</v>
+      <c r="AI73" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -7692,22 +11496,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_37.jpg</t>
+          <t>stimuli/hand/hand_33.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,7 +11526,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7759,16 +11563,68 @@
       <c r="S74" t="n">
         <v>9</v>
       </c>
-      <c r="T74" t="n">
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF74" t="n">
         <v>8</v>
       </c>
-      <c r="U74" t="n">
-        <v>1</v>
-      </c>
-      <c r="V74" t="n">
-        <v>13</v>
-      </c>
-      <c r="W74" t="n">
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI74" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7791,22 +11647,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/ball/ball_03.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7858,16 +11714,68 @@
       <c r="S75" t="n">
         <v>10</v>
       </c>
-      <c r="T75" t="n">
-        <v>1</v>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
       </c>
       <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
         <v>2</v>
       </c>
-      <c r="V75" t="n">
+      <c r="AH75" t="n">
         <v>5</v>
       </c>
-      <c r="W75" t="n">
+      <c r="AI75" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7890,22 +11798,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7925,7 +11833,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7957,17 +11865,69 @@
       <c r="S76" t="n">
         <v>11</v>
       </c>
-      <c r="T76" t="n">
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF76" t="n">
         <v>2</v>
       </c>
-      <c r="U76" t="n">
+      <c r="AG76" t="n">
         <v>7</v>
       </c>
-      <c r="V76" t="n">
+      <c r="AH76" t="n">
         <v>6</v>
       </c>
-      <c r="W76" t="n">
-        <v>15</v>
+      <c r="AI76" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="77">
@@ -7989,22 +11949,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_41.jpg</t>
+          <t>stimuli/hammer/hammer_32.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_05.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/house/house_29.jpg</t>
+          <t>stimuli/house/house_09.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8056,16 +12016,68 @@
       <c r="S77" t="n">
         <v>12</v>
       </c>
-      <c r="T77" t="n">
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF77" t="n">
         <v>7</v>
       </c>
-      <c r="U77" t="n">
+      <c r="AG77" t="n">
         <v>6</v>
       </c>
-      <c r="V77" t="n">
+      <c r="AH77" t="n">
         <v>14</v>
       </c>
-      <c r="W77" t="n">
+      <c r="AI77" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8088,22 +12100,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_29.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/dog/dog_24.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_47.jpg</t>
+          <t>stimuli/jacket/jacket_41.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8113,7 +12125,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -8155,16 +12167,68 @@
       <c r="S78" t="n">
         <v>13</v>
       </c>
-      <c r="T78" t="n">
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF78" t="n">
         <v>6</v>
       </c>
-      <c r="U78" t="n">
-        <v>11</v>
-      </c>
-      <c r="V78" t="n">
+      <c r="AG78" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH78" t="n">
         <v>5</v>
       </c>
-      <c r="W78" t="n">
+      <c r="AI78" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8187,42 +12251,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/car/car_02.jpg</t>
+          <t>stimuli/phone/phone_01.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/key/key_29.jpg</t>
+          <t>stimuli/boat/boat_01.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/bread/bread_43.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_02.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8254,17 +12318,69 @@
       <c r="S79" t="n">
         <v>14</v>
       </c>
-      <c r="T79" t="n">
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_01.jpg</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="AA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_01.jpg</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>stimuli/boat/boat_01.jpg</t>
+        </is>
+      </c>
+      <c r="AF79" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI79" t="n">
         <v>11</v>
-      </c>
-      <c r="U79" t="n">
-        <v>15</v>
-      </c>
-      <c r="V79" t="n">
-        <v>3</v>
-      </c>
-      <c r="W79" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
